--- a/pesquisa-2-deveres-sociais/docs/02-lista-de-praticas/Lista_de_Praticas_Rastreabilidade.xlsx
+++ b/pesquisa-2-deveres-sociais/docs/02-lista-de-praticas/Lista_de_Praticas_Rastreabilidade.xlsx
@@ -505,7 +505,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Gerado por construir_praticas.py em 2026-10-10.</t>
+          <t>Gerado por construir_praticas.py em 2026-10-11.</t>
         </is>
       </c>
     </row>
